--- a/tests/resources/EVA_Submission_test.xlsx
+++ b/tests/resources/EVA_Submission_test.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nkumar2/PycharmProjects/eva-sub-cli/tests/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D628AC7-3401-8248-A22E-D960140ADCEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D92FA1-B226-3341-86B7-E9B4FF75CECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLEASE READ FIRST" sheetId="1" r:id="rId1"/>
     <sheet name="Submitter Details" sheetId="2" r:id="rId2"/>
-    <sheet name="Data Acknowledgement" sheetId="12" r:id="rId3"/>
+    <sheet name="Statements" sheetId="12" r:id="rId3"/>
     <sheet name="Project HELP" sheetId="3" r:id="rId4"/>
     <sheet name="Project" sheetId="4" r:id="rId5"/>
     <sheet name="Analysis HELP" sheetId="5" r:id="rId6"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="603">
   <si>
     <t>PLEASE READ FIRST</t>
   </si>
@@ -1986,6 +1986,9 @@
   </si>
   <si>
     <t>V3.1.0 Sep 2026</t>
+  </si>
+  <si>
+    <t>Statements</t>
   </si>
 </sst>
 </file>
@@ -2576,6 +2579,9 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2599,9 +2605,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2905,8 +2908,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1025" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="69"/>
-      <c r="B1" s="69"/>
+      <c r="A1" s="70"/>
+      <c r="B1" s="70"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -2915,10 +2918,10 @@
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:1025" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="70"/>
+      <c r="B2" s="71"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2927,10 +2930,10 @@
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="72" t="s">
         <v>601</v>
       </c>
-      <c r="B3" s="71"/>
+      <c r="B3" s="72"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -2939,10 +2942,10 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="72"/>
+      <c r="B4" s="73"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2951,10 +2954,10 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="73"/>
+      <c r="B5" s="74"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -4004,8 +4007,8 @@
       <c r="AMK7" s="5"/>
     </row>
     <row r="8" spans="1:1025" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="69"/>
-      <c r="B8" s="69"/>
+      <c r="A8" s="70"/>
+      <c r="B8" s="70"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -5031,10 +5034,10 @@
       <c r="AMK8" s="5"/>
     </row>
     <row r="9" spans="1:1025" ht="19" x14ac:dyDescent="0.25">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="76" t="s">
         <v>594</v>
       </c>
-      <c r="B9" s="75"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -6060,8 +6063,8 @@
       <c r="AMK9" s="5"/>
     </row>
     <row r="10" spans="1:1025" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="69"/>
-      <c r="B10" s="69"/>
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -7087,10 +7090,10 @@
       <c r="AMK10" s="5"/>
     </row>
     <row r="11" spans="1:1025" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="76"/>
+      <c r="B11" s="77"/>
     </row>
     <row r="12" spans="1:1025" ht="20" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
@@ -7111,7 +7114,7 @@
     </row>
     <row r="14" spans="1:1025" ht="60" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B14" s="64" t="s">
         <v>596</v>
@@ -7150,10 +7153,10 @@
       </c>
     </row>
     <row r="20" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="74"/>
+      <c r="B20" s="75"/>
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
@@ -8179,25 +8182,25 @@
       <c r="AMK20"/>
     </row>
     <row r="21" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="74" t="s">
+      <c r="A21" s="75" t="s">
         <v>597</v>
       </c>
-      <c r="B21" s="74"/>
+      <c r="B21" s="75"/>
     </row>
     <row r="22" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="74" t="s">
+      <c r="A22" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="74"/>
+      <c r="B22" s="75"/>
     </row>
     <row r="23" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="74"/>
+      <c r="B23" s="75"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NtYCE6A6tGxk8QiiUUim3LFH9ql/O0pU7INH89Q4Dy/whC7ueYuZLI5W6jY51G90hBBvk0JyAhtVw0g55HYx7A==" saltValue="pWtsgMocKN/p6OPC/94y8g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="cT4ofnJLIvdWQ8BEbJzHJr/tNn4WvtpHrRBzeoDKTN7sSb+CPI/KyDEVkicPOMFFIlrwb8QhiEn/pksjKVh7WA==" saltValue="LaD9EAaB/PQc/QsDzdnEtA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="13">
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
@@ -10087,10 +10090,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="69" t="s">
         <v>595</v>
       </c>
-      <c r="B1" s="77"/>
+      <c r="B1" s="69"/>
     </row>
     <row r="2" spans="1:2" s="66" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="65" t="s">

--- a/tests/resources/EVA_Submission_test.xlsx
+++ b/tests/resources/EVA_Submission_test.xlsx
@@ -2579,11 +2579,17 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2597,14 +2603,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2612,14 +2612,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2918,10 +2918,10 @@
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:1025" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="71"/>
+      <c r="B2" s="73"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2930,10 +2930,10 @@
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="74" t="s">
         <v>601</v>
       </c>
-      <c r="B3" s="72"/>
+      <c r="B3" s="74"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -2942,10 +2942,10 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="73"/>
+      <c r="B4" s="75"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2954,10 +2954,10 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="74"/>
+      <c r="B5" s="76"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -5034,10 +5034,10 @@
       <c r="AMK8" s="5"/>
     </row>
     <row r="9" spans="1:1025" ht="19" x14ac:dyDescent="0.25">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="71" t="s">
         <v>594</v>
       </c>
-      <c r="B9" s="76"/>
+      <c r="B9" s="71"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -7090,10 +7090,10 @@
       <c r="AMK10" s="5"/>
     </row>
     <row r="11" spans="1:1025" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="77"/>
+      <c r="B11" s="72"/>
     </row>
     <row r="12" spans="1:1025" ht="20" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
@@ -7153,10 +7153,10 @@
       </c>
     </row>
     <row r="20" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="75" t="s">
+      <c r="A20" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="75"/>
+      <c r="B20" s="69"/>
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
@@ -8182,26 +8182,31 @@
       <c r="AMK20"/>
     </row>
     <row r="21" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="69" t="s">
         <v>597</v>
       </c>
-      <c r="B21" s="75"/>
+      <c r="B21" s="69"/>
     </row>
     <row r="22" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="75" t="s">
+      <c r="A22" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="75"/>
+      <c r="B22" s="69"/>
     </row>
     <row r="23" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="75"/>
+      <c r="B23" s="69"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="cT4ofnJLIvdWQ8BEbJzHJr/tNn4WvtpHrRBzeoDKTN7sSb+CPI/KyDEVkicPOMFFIlrwb8QhiEn/pksjKVh7WA==" saltValue="LaD9EAaB/PQc/QsDzdnEtA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="13">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
@@ -8210,11 +8215,6 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -10090,10 +10090,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="77" t="s">
         <v>595</v>
       </c>
-      <c r="B1" s="69"/>
+      <c r="B1" s="77"/>
     </row>
     <row r="2" spans="1:2" s="66" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="65" t="s">
@@ -11239,10 +11239,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="82" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="80"/>
+      <c r="B1" s="82"/>
       <c r="C1" s="78"/>
       <c r="D1" s="42" t="s">
         <v>215</v>
@@ -11308,16 +11308,16 @@
       <c r="I2" s="81"/>
       <c r="J2" s="81"/>
       <c r="K2" s="81"/>
-      <c r="L2" s="82" t="s">
+      <c r="L2" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82" t="s">
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80" t="s">
         <v>142</v>
       </c>
-      <c r="P2" s="82"/>
-      <c r="Q2" s="82"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
       <c r="R2" s="81" t="s">
         <v>149</v>
       </c>
@@ -11561,16 +11561,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="Z2:AI2"/>
     <mergeCell ref="AJ2:AS2"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="L2:N2"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Metadata and VCF" prompt="These sample names must match those provided in the VCF file(s)" sqref="E1 B4:B1003" xr:uid="{00000000-0002-0000-0700-000000000000}">
